--- a/contoh_format_upload_peternakan.xlsx
+++ b/contoh_format_upload_peternakan.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Peternakan" sheetId="1" r:id="Rd6850212a6fb41d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="Ra505e0a24bdb4d96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Peternakan" sheetId="1" r:id="R2f37d94a506e4e31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R3387a51bc95140c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -265,7 +265,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
@@ -586,7 +586,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd509ba46c38c44e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc36b2278477b4c23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -595,7 +595,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="110" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="115" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -620,7 +620,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>4. jenis_ternak disarankan: Sapi Perah, Sapi Potong, Sapi, Kerbau, Kambing, Domba, Ayam, Ayam Buras, Ayam Ras Pedaging, Ayam Ras Petelur, Itik, Lainnya.</x:v>
+        <x:v>4. luas_lahan_ha sangat disarankan agar aplikasi bisa menghitung kepadatan ternak.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">

--- a/contoh_format_upload_peternakan.xlsx
+++ b/contoh_format_upload_peternakan.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Peternakan" sheetId="1" r:id="R2f37d94a506e4e31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R3387a51bc95140c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Peternakan" sheetId="1" r:id="R14c8050b03194ba7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R1ae664c493544844"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -31,8 +31,19 @@
       <x:color rgb="FF111827"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -44,6 +55,26 @@
         <x:fgColor rgb="FF16A34A"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFEF3C7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF59E0B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFBEB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -52,7 +83,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -85,6 +116,29 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -314,7 +368,7 @@
       <x:c r="J1" s="6" t="str">
         <x:v>jumlah_ekor</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="K1" s="20" t="str">
         <x:v>luas_lahan_ha</x:v>
       </x:c>
       <x:c r="L1" s="6" t="str">
@@ -364,7 +418,7 @@
       <x:c r="J2" s="12" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="n">
+      <x:c r="K2" s="24" t="n">
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="L2" s="12" t="str">
@@ -414,7 +468,7 @@
       <x:c r="J3" s="12" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K3" s="12" t="n">
+      <x:c r="K3" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="L3" s="12" t="str">
@@ -464,7 +518,7 @@
       <x:c r="J4" s="12" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="K4" s="12" t="n">
+      <x:c r="K4" s="24" t="n">
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="L4" s="12" t="str">
@@ -514,7 +568,7 @@
       <x:c r="J5" s="12" t="n">
         <x:v>2500</x:v>
       </x:c>
-      <x:c r="K5" s="12" t="n">
+      <x:c r="K5" s="24" t="n">
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="L5" s="12" t="str">
@@ -564,7 +618,7 @@
       <x:c r="J6" s="12" t="n">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="K6" s="12" t="n">
+      <x:c r="K6" s="24" t="n">
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="L6" s="12" t="str">
@@ -586,7 +640,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc36b2278477b4c23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dcdc8bee81d4def"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -595,11 +649,11 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="115" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="120" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="14" t="str">
+      <x:c r="A1" s="17" t="str">
         <x:v>Petunjuk Upload XLSX</x:v>
       </x:c>
     </x:row>
@@ -614,18 +668,28 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="12" t="str">
+      <x:c r="A4" s="19" t="str">
         <x:v>3. jumlah_ekor wajib angka polos, contoh 2500, bukan 2.500 atau 2,500.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="12" t="str">
-        <x:v>4. luas_lahan_ha sangat disarankan agar aplikasi bisa menghitung kepadatan ternak.</x:v>
+      <x:c r="A5" s="19" t="str">
+        <x:v>4. Tambahkan luas_lahan_ha pada CSV/XLSX untuk insight lebih baik.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="12" t="str">
-        <x:v>5. Untuk NDVI, gunakan koordinat kandang/lahan hijauan/pakan yang benar-benar aktual.</x:v>
+      <x:c r="A6" s="19" t="str">
+        <x:v>5. Kolom luas_lahan_ha dipakai untuk menghitung kepadatan ternak per hektare.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="12" t="str">
+        <x:v>6. Contoh: jika 75 ekor sapi berada pada lahan 1.5 ha, aplikasi dapat menghitung ±50 ekor/ha.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12" t="str">
+        <x:v>7. Untuk NDVI, gunakan koordinat kandang/lahan hijauan/pakan yang benar-benar aktual.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
